--- a/artfynd/A 35963-2026 artfynd.xlsx
+++ b/artfynd/A 35963-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191271</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136191109</v>
       </c>
       <c r="B3" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136191210</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136191349</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136191468</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136191187</v>
       </c>
       <c r="B7" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136191159</v>
       </c>
       <c r="B8" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136191401</v>
       </c>
       <c r="B9" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2026 artfynd.xlsx
+++ b/artfynd/A 35963-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191271</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136191109</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136191210</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136191349</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136191468</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136191187</v>
       </c>
       <c r="B7" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136191159</v>
       </c>
       <c r="B8" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136191401</v>
       </c>
       <c r="B9" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2026 artfynd.xlsx
+++ b/artfynd/A 35963-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191271</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136191109</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136191210</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136191349</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136191468</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136191187</v>
       </c>
       <c r="B7" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136191159</v>
       </c>
       <c r="B8" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136191401</v>
       </c>
       <c r="B9" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2026 artfynd.xlsx
+++ b/artfynd/A 35963-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191271</v>
       </c>
       <c r="B2" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136191109</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136191210</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136191349</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136191468</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136191187</v>
       </c>
       <c r="B7" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136191159</v>
       </c>
       <c r="B8" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136191401</v>
       </c>
       <c r="B9" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2026 artfynd.xlsx
+++ b/artfynd/A 35963-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191271</v>
       </c>
       <c r="B2" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136191109</v>
       </c>
       <c r="B3" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136191210</v>
       </c>
       <c r="B4" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136191349</v>
       </c>
       <c r="B5" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136191468</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136191187</v>
       </c>
       <c r="B7" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136191159</v>
       </c>
       <c r="B8" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136191401</v>
       </c>
       <c r="B9" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35963-2026 artfynd.xlsx
+++ b/artfynd/A 35963-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191271</v>
       </c>
       <c r="B2" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136191109</v>
       </c>
       <c r="B3" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136191210</v>
       </c>
       <c r="B4" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136191349</v>
       </c>
       <c r="B5" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136191468</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136191187</v>
       </c>
       <c r="B7" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136191159</v>
       </c>
       <c r="B8" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136191401</v>
       </c>
       <c r="B9" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
